--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,26 +807,26 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -874,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1110,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E12" s="3">
         <v>6000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G12" s="3">
         <v>4100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>7100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>6500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>800</v>
       </c>
       <c r="S12" s="3">
         <v>900</v>
       </c>
       <c r="T12" s="3">
+        <v>800</v>
+      </c>
+      <c r="U12" s="3">
+        <v>900</v>
+      </c>
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>200</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>100</v>
       </c>
       <c r="AA12" s="3">
         <v>300</v>
       </c>
       <c r="AB12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
         <v>100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1296,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1347,13 +1386,19 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-200</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,97 +1522,105 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F17" s="3">
         <v>8600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>-100</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1569,88 +1628,94 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-6500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-6500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-6400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-9000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1691,32 +1758,32 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>600</v>
+      </c>
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1724,14 +1791,14 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1768,11 +1835,17 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1860,16 +1933,22 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F22" s="3">
         <v>600</v>
@@ -1878,13 +1957,13 @@
         <v>600</v>
       </c>
       <c r="H22" s="3">
+        <v>600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>600</v>
+      </c>
+      <c r="J22" s="3">
         <v>500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
@@ -1893,14 +1972,14 @@
         <v>400</v>
       </c>
       <c r="M22" s="3">
+        <v>500</v>
+      </c>
+      <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,11 +1992,11 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1949,97 +2028,109 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2759,32 +2898,32 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2792,14 +2931,14 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2836,100 +2975,112 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F41" s="3">
         <v>41800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>47800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>51000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>57400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>61200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>66700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>74800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>84500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>39500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>45300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>22000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>24300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>9400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1800</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,97 +3623,109 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>400</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>300</v>
       </c>
       <c r="AB43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC43" s="3">
         <v>300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
+      <c r="AD43" s="3">
+        <v>300</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3622,186 +3813,204 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4300</v>
       </c>
       <c r="J45" s="3">
         <v>4700</v>
       </c>
       <c r="K45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M45" s="3">
         <v>2300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
+      <c r="AD45" s="3">
+        <v>0</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>39900</v>
+      </c>
+      <c r="F46" s="3">
         <v>45600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>52600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>56900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>64700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>66700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>70500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>77100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>82600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>90900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>44000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>49200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>24000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>26100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>8700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>10800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2100</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3889,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3898,10 +4113,10 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G48" s="3">
         <v>500</v>
@@ -3910,28 +4125,28 @@
         <v>500</v>
       </c>
       <c r="I48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="K48" s="3">
         <v>700</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
       </c>
       <c r="O48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
@@ -3948,11 +4163,11 @@
       <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>200</v>
+      </c>
+      <c r="W48" s="3">
+        <v>200</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3963,11 +4178,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4055,11 +4276,11 @@
       <c r="AA49" s="3">
         <v>16500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
+      <c r="AB49" s="3">
+        <v>16500</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>16500</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4478,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4277,11 +4516,11 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -4295,11 +4534,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F54" s="3">
         <v>62700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>69700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>74000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>81800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>83800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>87800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>94400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>99900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>107700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>60700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>65900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>40700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>42800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>23700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>24500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>25400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>27500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>23600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>17400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>17700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>18200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>18800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>18400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2100</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,121 +4837,129 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>500</v>
       </c>
       <c r="V57" s="3">
         <v>500</v>
       </c>
       <c r="W57" s="3">
+        <v>500</v>
+      </c>
+      <c r="X57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y57" s="3">
         <v>800</v>
-      </c>
-      <c r="X57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>200</v>
       </c>
       <c r="Z57" s="3">
         <v>200</v>
       </c>
       <c r="AA57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
+      <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>200</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F58" s="3">
         <v>10000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>10000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2500</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,11 +4969,11 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4756,8 +5023,14 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4765,216 +5038,228 @@
         <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G59" s="3">
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>600</v>
       </c>
       <c r="N59" s="3">
         <v>600</v>
       </c>
       <c r="O59" s="3">
+        <v>600</v>
+      </c>
+      <c r="P59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>400</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F60" s="3">
         <v>14400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
-      </c>
-      <c r="X60" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>200</v>
       </c>
       <c r="Z60" s="3">
         <v>200</v>
       </c>
       <c r="AA60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
+      <c r="AC60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>200</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>2400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>12100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>14600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>14500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>14500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>14400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>14300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5023,43 +5308,49 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1100</v>
       </c>
       <c r="H62" s="3">
         <v>1100</v>
       </c>
       <c r="I62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -5071,10 +5362,10 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>200</v>
@@ -5082,11 +5373,11 @@
       <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>200</v>
+      </c>
+      <c r="W62" s="3">
+        <v>200</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -5100,20 +5391,26 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="3">
         <v>100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F66" s="3">
         <v>18000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>19100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>21700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>20100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>17900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>19700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>19400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>800</v>
-      </c>
-      <c r="X66" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>200</v>
       </c>
       <c r="Z66" s="3">
         <v>200</v>
       </c>
       <c r="AA66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
+      <c r="AC66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>200</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-132000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-112600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-104100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-97600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-91000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-85200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-77500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-70600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-63700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-54000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-44600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-37900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-33400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-25500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-23300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-21300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-19000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-15900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-15500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-13600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-700</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F76" s="3">
         <v>44700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>50700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>55300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>60100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>63700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>69900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>75600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>80200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>88300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>43200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>63600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>38800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>41200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>21700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>23600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>24700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>26800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>22900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>16500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>17500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>18000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>18600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>18100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7983,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7619,8 +8078,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,20 +8493,26 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -8032,112 +8523,118 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>52900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>15000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>28500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>23200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>5000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>7300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -8183,96 +8680,108 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-8100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>45000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>23400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>19500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>5900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -813,22 +817,22 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E12" s="3">
         <v>8700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>6000</v>
       </c>
       <c r="F12" s="3">
         <v>6000</v>
       </c>
       <c r="G12" s="3">
-        <v>4100</v>
+        <v>6000</v>
       </c>
       <c r="H12" s="3">
         <v>4100</v>
       </c>
       <c r="I12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J12" s="3">
         <v>3400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>300</v>
       </c>
-      <c r="AD12" s="3">
-        <v>0</v>
-      </c>
       <c r="AE12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1392,13 +1412,16 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,103 +1550,107 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E17" s="3">
         <v>11000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6500</v>
       </c>
       <c r="H17" s="3">
         <v>6500</v>
       </c>
       <c r="I17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4800</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2100</v>
       </c>
       <c r="T17" s="3">
         <v>2100</v>
       </c>
       <c r="U17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
-      </c>
-      <c r="X17" s="3">
-        <v>1900</v>
       </c>
       <c r="Y17" s="3">
         <v>1900</v>
       </c>
       <c r="Z17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>-100</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,94 +1658,97 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-6500</v>
       </c>
       <c r="H18" s="3">
         <v>-6500</v>
       </c>
       <c r="I18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-6400</v>
       </c>
       <c r="L18" s="3">
         <v>-6400</v>
       </c>
       <c r="M18" s="3">
-        <v>-9000</v>
+        <v>-6400</v>
       </c>
       <c r="N18" s="3">
         <v>-9000</v>
       </c>
       <c r="O18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2100</v>
       </c>
       <c r="T18" s="3">
         <v>-2100</v>
       </c>
       <c r="U18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V18" s="3">
         <v>-2300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y18" s="3">
         <v>-1900</v>
       </c>
       <c r="Z18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,35 +1792,35 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>600</v>
       </c>
       <c r="G20" s="3">
         <v>600</v>
       </c>
       <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1797,11 +1831,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1841,11 +1875,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1939,19 +1976,22 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>600</v>
       </c>
       <c r="G22" s="3">
         <v>600</v>
@@ -1963,26 +2003,26 @@
         <v>600</v>
       </c>
       <c r="J22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
       </c>
       <c r="L22" s="3">
+        <v>500</v>
+      </c>
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1998,8 +2038,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2034,103 +2074,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6500</v>
       </c>
       <c r="H23" s="3">
         <v>-6500</v>
       </c>
       <c r="I23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-2100</v>
       </c>
       <c r="T23" s="3">
         <v>-2100</v>
       </c>
       <c r="U23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y23" s="3">
         <v>-1900</v>
       </c>
       <c r="Z23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-6500</v>
       </c>
       <c r="H26" s="3">
         <v>-6500</v>
       </c>
       <c r="I26" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-2100</v>
       </c>
       <c r="T26" s="3">
         <v>-2100</v>
       </c>
       <c r="U26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y26" s="3">
         <v>-1900</v>
       </c>
       <c r="Z26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-6500</v>
       </c>
       <c r="H27" s="3">
         <v>-6500</v>
       </c>
       <c r="I27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-2100</v>
       </c>
       <c r="T27" s="3">
         <v>-2100</v>
       </c>
       <c r="U27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V27" s="3">
         <v>-2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y27" s="3">
         <v>-1900</v>
       </c>
       <c r="Z27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2898,35 +2968,35 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-600</v>
       </c>
       <c r="G32" s="3">
         <v>-600</v>
       </c>
       <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2937,11 +3007,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2981,106 +3051,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-6500</v>
       </c>
       <c r="H33" s="3">
         <v>-6500</v>
       </c>
       <c r="I33" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-2100</v>
       </c>
       <c r="T33" s="3">
         <v>-2100</v>
       </c>
       <c r="U33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V33" s="3">
         <v>-2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y33" s="3">
         <v>-1900</v>
       </c>
       <c r="Z33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-6500</v>
       </c>
       <c r="H35" s="3">
         <v>-6500</v>
       </c>
       <c r="I35" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-2100</v>
       </c>
       <c r="T35" s="3">
         <v>-2100</v>
       </c>
       <c r="U35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V35" s="3">
         <v>-2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y35" s="3">
         <v>-1900</v>
       </c>
       <c r="Z35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3525,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E41" s="3">
         <v>26000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>61200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1800</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,94 +3719,97 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>200</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>300</v>
       </c>
       <c r="AD43" s="3">
         <v>300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
+      <c r="AE43" s="3">
+        <v>300</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,94 +3915,97 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
+        <v>300</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
+      <c r="AE45" s="3">
+        <v>0</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
@@ -3914,103 +4013,109 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E46" s="3">
         <v>29800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>39900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>77100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>82600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>90900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>26100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,8 +4209,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4119,7 +4227,7 @@
         <v>400</v>
       </c>
       <c r="G48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>500</v>
@@ -4131,7 +4239,7 @@
         <v>500</v>
       </c>
       <c r="K48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L48" s="3">
         <v>700</v>
@@ -4140,7 +4248,7 @@
         <v>700</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
@@ -4149,7 +4257,7 @@
         <v>100</v>
       </c>
       <c r="Q48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
@@ -4169,8 +4277,8 @@
       <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>200</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -4184,8 +4292,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4282,8 +4393,8 @@
       <c r="AC49" s="3">
         <v>16500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
+      <c r="AD49" s="3">
+        <v>16500</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4522,8 +4642,8 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -4540,8 +4660,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E54" s="3">
         <v>46800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>57000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>81800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>83800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>87800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>60700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>65900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2100</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4969,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4848,58 +4979,58 @@
         <v>9400</v>
       </c>
       <c r="E57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1600</v>
       </c>
       <c r="Q57" s="3">
         <v>1600</v>
       </c>
       <c r="R57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S57" s="3">
         <v>1200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>800</v>
       </c>
       <c r="T57" s="3">
         <v>800</v>
       </c>
       <c r="U57" s="3">
+        <v>800</v>
+      </c>
+      <c r="V57" s="3">
         <v>700</v>
-      </c>
-      <c r="V57" s="3">
-        <v>500</v>
       </c>
       <c r="W57" s="3">
         <v>500</v>
@@ -4908,10 +5039,10 @@
         <v>500</v>
       </c>
       <c r="Y57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z57" s="3">
         <v>800</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
@@ -4920,49 +5051,52 @@
         <v>200</v>
       </c>
       <c r="AC57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>10000</v>
       </c>
       <c r="G58" s="3">
         <v>10000</v>
       </c>
       <c r="H58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I58" s="3">
         <v>7500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4975,8 +5109,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -5029,13 +5163,16 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>600</v>
@@ -5044,7 +5181,7 @@
         <v>600</v>
       </c>
       <c r="G59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H59" s="3">
         <v>700</v>
@@ -5053,19 +5190,19 @@
         <v>700</v>
       </c>
       <c r="J59" s="3">
+        <v>700</v>
+      </c>
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
-      </c>
-      <c r="N59" s="3">
-        <v>600</v>
       </c>
       <c r="O59" s="3">
         <v>600</v>
@@ -5074,20 +5211,20 @@
         <v>600</v>
       </c>
       <c r="Q59" s="3">
+        <v>600</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
@@ -5095,11 +5232,11 @@
         <v>0</v>
       </c>
       <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,14 +5246,14 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
+      <c r="AE59" s="3">
+        <v>0</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
@@ -5124,79 +5261,82 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E60" s="3">
         <v>17500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
-      </c>
-      <c r="V60" s="3">
-        <v>500</v>
       </c>
       <c r="W60" s="3">
         <v>500</v>
       </c>
       <c r="X60" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Y60" s="3">
         <v>800</v>
       </c>
       <c r="Z60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AA60" s="3">
         <v>200</v>
@@ -5205,22 +5345,25 @@
         <v>200</v>
       </c>
       <c r="AC60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD60" s="3">
         <v>300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5231,38 +5374,38 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>2400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>14500</v>
       </c>
       <c r="M61" s="3">
         <v>14500</v>
       </c>
       <c r="N61" s="3">
+        <v>14500</v>
+      </c>
+      <c r="O61" s="3">
         <v>14400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5314,25 +5457,28 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>1200</v>
       </c>
       <c r="H62" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I62" s="3">
         <v>1100</v>
@@ -5341,19 +5487,19 @@
         <v>1100</v>
       </c>
       <c r="K62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="L62" s="3">
         <v>1000</v>
       </c>
       <c r="M62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -5368,7 +5514,7 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -5379,8 +5525,8 @@
       <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>200</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -5397,20 +5543,23 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" s="3">
         <v>100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,79 +5849,82 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E66" s="3">
         <v>17800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
-      </c>
-      <c r="V66" s="3">
-        <v>700</v>
       </c>
       <c r="W66" s="3">
         <v>700</v>
       </c>
       <c r="X66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Y66" s="3">
         <v>800</v>
       </c>
       <c r="Z66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AA66" s="3">
         <v>200</v>
@@ -5775,22 +5933,25 @@
         <v>200</v>
       </c>
       <c r="AC66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD66" s="3">
         <v>300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-141800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-132000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-121000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-112600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-104100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-97600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-91000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-85200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-77500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-70600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-63700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-54000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-44600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-33400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-25500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-23300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-21300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-19000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-15900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-700</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E76" s="3">
         <v>29000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>55300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>63700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>69900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>75600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>88300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>63600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1900</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-6500</v>
       </c>
       <c r="H81" s="3">
         <v>-6500</v>
       </c>
       <c r="I81" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-2100</v>
       </c>
       <c r="T81" s="3">
         <v>-2100</v>
       </c>
       <c r="U81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V81" s="3">
         <v>-2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1900</v>
       </c>
       <c r="Y81" s="3">
         <v>-1900</v>
       </c>
       <c r="Z81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-100</v>
       </c>
       <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,23 +8742,26 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2500</v>
+        <v>13000</v>
       </c>
       <c r="E100" s="3">
         <v>-2500</v>
       </c>
       <c r="F100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -8529,32 +8775,32 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>52900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>23200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8562,14 +8808,14 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>5000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7300</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8577,37 +8823,40 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>400</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -8615,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>100</v>
       </c>
       <c r="M101" s="3">
         <v>100</v>
       </c>
       <c r="N101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8686,102 +8935,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9800</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-6000</v>
       </c>
       <c r="F102" s="3">
         <v>-6000</v>
       </c>
       <c r="G102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H102" s="3">
         <v>-3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>45000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19500</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-1100</v>
       </c>
       <c r="T102" s="3">
         <v>-1100</v>
       </c>
       <c r="U102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5900</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-500</v>
       </c>
       <c r="Z102" s="3">
         <v>-500</v>
       </c>
       <c r="AA102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,156 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -820,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -894,8 +898,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -992,8 +999,11 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,20 +1013,20 @@
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1100,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,106 +1139,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E12" s="3">
         <v>7100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>6000</v>
       </c>
       <c r="G12" s="3">
         <v>6000</v>
       </c>
       <c r="H12" s="3">
-        <v>4100</v>
+        <v>6000</v>
       </c>
       <c r="I12" s="3">
         <v>4100</v>
       </c>
       <c r="J12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K12" s="3">
         <v>3400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AE12" s="3">
-        <v>0</v>
-      </c>
       <c r="AF12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="3">
         <v>100</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,31 +1339,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1415,13 +1435,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-200</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E17" s="3">
         <v>9900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>6500</v>
       </c>
       <c r="I17" s="3">
         <v>6500</v>
       </c>
       <c r="J17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K17" s="3">
         <v>5700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>2100</v>
       </c>
       <c r="U17" s="3">
         <v>2100</v>
       </c>
       <c r="V17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1900</v>
       </c>
       <c r="Z17" s="3">
         <v>1900</v>
       </c>
       <c r="AA17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>-100</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-12300</v>
       </c>
       <c r="E18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-8600</v>
-      </c>
       <c r="H18" s="3">
-        <v>-6500</v>
+        <v>-8500</v>
       </c>
       <c r="I18" s="3">
-        <v>-6500</v>
+        <v>-6400</v>
       </c>
       <c r="J18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-6400</v>
       </c>
       <c r="M18" s="3">
         <v>-6400</v>
       </c>
       <c r="N18" s="3">
-        <v>-9000</v>
+        <v>-6400</v>
       </c>
       <c r="O18" s="3">
         <v>-9000</v>
       </c>
       <c r="P18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4800</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-2100</v>
       </c>
       <c r="U18" s="3">
         <v>-2100</v>
       </c>
       <c r="V18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z18" s="3">
         <v>-1900</v>
       </c>
       <c r="AA18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,8 +1816,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1792,38 +1826,38 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
-        <v>500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1834,11 +1868,11 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1878,34 +1912,37 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1979,22 +2016,25 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>600</v>
       </c>
       <c r="H22" s="3">
         <v>600</v>
@@ -2006,26 +2046,26 @@
         <v>600</v>
       </c>
       <c r="K22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
       </c>
       <c r="M22" s="3">
+        <v>500</v>
+      </c>
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,8 +2081,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2077,129 +2117,135 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-6500</v>
       </c>
       <c r="I23" s="3">
         <v>-6500</v>
       </c>
       <c r="J23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-2100</v>
       </c>
       <c r="U23" s="3">
         <v>-2100</v>
       </c>
       <c r="V23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z23" s="3">
         <v>-1900</v>
       </c>
       <c r="AA23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2273,8 +2319,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-6500</v>
       </c>
       <c r="I26" s="3">
         <v>-6500</v>
       </c>
       <c r="J26" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-2100</v>
       </c>
       <c r="U26" s="3">
         <v>-2100</v>
       </c>
       <c r="V26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z26" s="3">
         <v>-1900</v>
       </c>
       <c r="AA26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-6500</v>
       </c>
       <c r="I27" s="3">
         <v>-6500</v>
       </c>
       <c r="J27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-2100</v>
       </c>
       <c r="U27" s="3">
         <v>-2100</v>
       </c>
       <c r="V27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z27" s="3">
         <v>-1900</v>
       </c>
       <c r="AA27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,8 +3026,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2968,38 +3038,38 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>400</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3010,11 +3080,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3054,109 +3124,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-6500</v>
       </c>
       <c r="I33" s="3">
         <v>-6500</v>
       </c>
       <c r="J33" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-2100</v>
       </c>
       <c r="U33" s="3">
         <v>-2100</v>
       </c>
       <c r="V33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z33" s="3">
         <v>-1900</v>
       </c>
       <c r="AA33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-6500</v>
       </c>
       <c r="I35" s="3">
         <v>-6500</v>
       </c>
       <c r="J35" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-2100</v>
       </c>
       <c r="U35" s="3">
         <v>-2100</v>
       </c>
       <c r="V35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z35" s="3">
         <v>-1900</v>
       </c>
       <c r="AA35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3612,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E41" s="3">
         <v>31100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>51000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1800</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,97 +3812,100 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>200</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>300</v>
       </c>
       <c r="AE43" s="3">
         <v>300</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
+      <c r="AF43" s="3">
+        <v>300</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>3</v>
@@ -3820,31 +3913,34 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3918,97 +4014,100 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R45" s="3">
         <v>1500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
       </c>
       <c r="V45" s="3">
+        <v>300</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
+      <c r="AF45" s="3">
+        <v>0</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
@@ -4016,129 +4115,135 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E46" s="3">
         <v>35500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>52600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>64700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>66700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>77100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>82600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>90900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>49200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>26100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2100</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4212,13 +4317,16 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>400</v>
@@ -4230,7 +4338,7 @@
         <v>400</v>
       </c>
       <c r="H48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I48" s="3">
         <v>500</v>
@@ -4242,7 +4350,7 @@
         <v>500</v>
       </c>
       <c r="L48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="M48" s="3">
         <v>700</v>
@@ -4251,7 +4359,7 @@
         <v>700</v>
       </c>
       <c r="O48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="P48" s="3">
         <v>100</v>
@@ -4260,7 +4368,7 @@
         <v>100</v>
       </c>
       <c r="R48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S48" s="3">
         <v>200</v>
@@ -4280,8 +4388,8 @@
       <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>200</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
@@ -4295,8 +4403,8 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4310,8 +4418,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4396,8 +4507,8 @@
       <c r="AD49" s="3">
         <v>16500</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
+      <c r="AE49" s="3">
+        <v>16500</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
@@ -4408,8 +4519,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,8 +4721,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4645,8 +4765,8 @@
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -4663,8 +4783,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E54" s="3">
         <v>52500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>57000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>81800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>83800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>87800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>60700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>65900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2100</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,70 +5100,71 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9400</v>
+        <v>10600</v>
       </c>
       <c r="E57" s="3">
-        <v>9400</v>
+        <v>9300</v>
       </c>
       <c r="F57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G57" s="3">
         <v>7900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="P57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>4200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1600</v>
       </c>
       <c r="R57" s="3">
         <v>1600</v>
       </c>
       <c r="S57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T57" s="3">
         <v>1200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>800</v>
       </c>
       <c r="U57" s="3">
         <v>800</v>
       </c>
       <c r="V57" s="3">
+        <v>800</v>
+      </c>
+      <c r="W57" s="3">
         <v>700</v>
-      </c>
-      <c r="W57" s="3">
-        <v>500</v>
       </c>
       <c r="X57" s="3">
         <v>500</v>
@@ -5042,10 +5173,10 @@
         <v>500</v>
       </c>
       <c r="Z57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA57" s="3">
         <v>800</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>200</v>
       </c>
       <c r="AB57" s="3">
         <v>200</v>
@@ -5054,52 +5185,55 @@
         <v>200</v>
       </c>
       <c r="AD57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5000</v>
+        <v>2600</v>
       </c>
       <c r="E58" s="3">
-        <v>7500</v>
+        <v>5100</v>
       </c>
       <c r="F58" s="3">
-        <v>9900</v>
+        <v>7600</v>
       </c>
       <c r="G58" s="3">
         <v>10000</v>
       </c>
       <c r="H58" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="I58" s="3">
-        <v>7500</v>
+        <v>10100</v>
       </c>
       <c r="J58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K58" s="3">
         <v>5000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5246,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5166,46 +5300,49 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="L59" s="3">
+        <v>900</v>
+      </c>
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
-        <v>600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
-        <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>700</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>600</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
@@ -5214,20 +5351,20 @@
         <v>600</v>
       </c>
       <c r="R59" s="3">
+        <v>600</v>
+      </c>
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
@@ -5235,11 +5372,11 @@
         <v>0</v>
       </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,14 +5386,14 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
+      <c r="AF59" s="3">
+        <v>0</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
@@ -5264,82 +5401,85 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E60" s="3">
         <v>15100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
-      </c>
-      <c r="W60" s="3">
-        <v>500</v>
       </c>
       <c r="X60" s="3">
         <v>500</v>
       </c>
       <c r="Y60" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Z60" s="3">
         <v>800</v>
       </c>
       <c r="AA60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -5348,67 +5488,70 @@
         <v>200</v>
       </c>
       <c r="AD60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE60" s="3">
         <v>300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>200</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G61" s="3">
-        <v>2400</v>
+        <v>400</v>
       </c>
       <c r="H61" s="3">
-        <v>4800</v>
+        <v>2800</v>
       </c>
       <c r="I61" s="3">
-        <v>7300</v>
+        <v>5300</v>
       </c>
       <c r="J61" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K61" s="3">
         <v>9700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>14500</v>
       </c>
       <c r="N61" s="3">
         <v>14500</v>
       </c>
       <c r="O61" s="3">
+        <v>14500</v>
+      </c>
+      <c r="P61" s="3">
         <v>14400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5460,49 +5603,52 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1200</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="J62" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="K62" s="3">
         <v>1100</v>
       </c>
       <c r="L62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="M62" s="3">
         <v>1000</v>
       </c>
       <c r="N62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -5517,7 +5663,7 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
         <v>200</v>
@@ -5528,8 +5674,8 @@
       <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
+      <c r="Y62" s="3">
+        <v>200</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
@@ -5546,20 +5692,23 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,82 +6007,85 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E66" s="3">
         <v>15400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
-      </c>
-      <c r="W66" s="3">
-        <v>700</v>
       </c>
       <c r="X66" s="3">
         <v>700</v>
       </c>
       <c r="Y66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z66" s="3">
         <v>800</v>
       </c>
       <c r="AA66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5936,22 +6094,25 @@
         <v>200</v>
       </c>
       <c r="AD66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE66" s="3">
         <v>300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6191,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-153900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-141800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-132000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-121000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-112600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-97600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-91000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-85200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-70600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-54000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-30200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-25500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-23300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-21300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-19000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-700</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>37100</v>
+        <v>38700</v>
       </c>
       <c r="E76" s="3">
-        <v>29000</v>
+        <v>36300</v>
       </c>
       <c r="F76" s="3">
-        <v>38100</v>
+        <v>28200</v>
       </c>
       <c r="G76" s="3">
-        <v>44700</v>
+        <v>37300</v>
       </c>
       <c r="H76" s="3">
+        <v>43900</v>
+      </c>
+      <c r="I76" s="3">
         <v>50700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>55300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>60100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>63700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>69900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>75600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>80200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>88300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>63600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1900</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-6500</v>
       </c>
       <c r="I81" s="3">
         <v>-6500</v>
       </c>
       <c r="J81" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-2100</v>
       </c>
       <c r="U81" s="3">
         <v>-2100</v>
       </c>
       <c r="V81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-1900</v>
       </c>
       <c r="Z81" s="3">
         <v>-1900</v>
       </c>
       <c r="AA81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,31 +7401,32 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7301,8 +7500,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-100</v>
       </c>
       <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,31 +8145,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8023,8 +8244,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,31 +8446,34 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8317,8 +8547,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,31 +8586,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,31 +8988,34 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E100" s="3">
         <v>13000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-2500</v>
       </c>
       <c r="F100" s="3">
         <v>-2500</v>
       </c>
       <c r="G100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8778,32 +9024,32 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>52900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>15000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>28500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>23200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -8811,14 +9057,14 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>5000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7300</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8826,25 +9072,28 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>400</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8852,43 +9101,43 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
       </c>
       <c r="N101" s="3">
         <v>100</v>
       </c>
       <c r="O101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8938,105 +9187,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>5100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9800</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-6000</v>
       </c>
       <c r="G102" s="3">
         <v>-6000</v>
       </c>
       <c r="H102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>45000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19500</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-1100</v>
       </c>
       <c r="U102" s="3">
         <v>-1100</v>
       </c>
       <c r="V102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5900</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-500</v>
       </c>
       <c r="AA102" s="3">
         <v>-500</v>
       </c>
       <c r="AB102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,166 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -827,26 +834,26 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -901,8 +908,14 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,22 +1015,28 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -1028,11 +1047,11 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -1103,8 +1122,14 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,109 +1165,117 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F12" s="3">
         <v>10100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>7100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>6000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>7100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>6500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2400</v>
-      </c>
-      <c r="U12" s="3">
-        <v>900</v>
-      </c>
-      <c r="V12" s="3">
-        <v>800</v>
       </c>
       <c r="W12" s="3">
         <v>900</v>
       </c>
       <c r="X12" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>200</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>100</v>
       </c>
       <c r="AE12" s="3">
         <v>300</v>
       </c>
       <c r="AF12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3">
         <v>100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>100</v>
       </c>
-      <c r="AI12" s="3" t="s">
+      <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1375,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1368,11 +1407,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1438,13 +1477,19 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-200</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1544,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F17" s="3">
         <v>12300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>11000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>-100</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-9900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-11000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-6400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-4800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,53 +1882,55 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-300</v>
+        <v>-600</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1871,14 +1938,14 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1915,41 +1982,47 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-9500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-10700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-8500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,28 +2092,34 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
@@ -2049,13 +2128,13 @@
         <v>600</v>
       </c>
       <c r="L22" s="3">
+        <v>600</v>
+      </c>
+      <c r="M22" s="3">
+        <v>600</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
@@ -2064,14 +2143,14 @@
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>500</v>
+      </c>
+      <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2084,11 +2163,11 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2120,109 +2199,121 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-9700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-11000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-8400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2247,11 +2338,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2322,8 +2413,14 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-11000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>100</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-11000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-8400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-5800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>100</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,53 +3162,59 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>300</v>
+        <v>600</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>300</v>
       </c>
       <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3083,14 +3222,14 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3127,112 +3266,124 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-11000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-5800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>100</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-11000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-5800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>100</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,109 +3784,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F41" s="3">
         <v>33600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>31100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>26000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>35800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>41800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>47800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>51000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>52200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>57400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>61200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>66700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>74800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>84500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>39500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>45300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>22000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>24300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1800</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,8 +3994,14 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3824,100 +4009,106 @@
         <v>1400</v>
       </c>
       <c r="E43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G43" s="3">
         <v>3400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>400</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>200</v>
       </c>
       <c r="AE43" s="3">
         <v>300</v>
       </c>
       <c r="AF43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG43" s="3">
         <v>300</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH43" s="3" t="s">
-        <v>3</v>
+      <c r="AH43" s="3">
+        <v>300</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3942,11 +4133,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4017,8 +4208,14 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4043,184 +4240,196 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>4100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4300</v>
       </c>
       <c r="N45" s="3">
         <v>4700</v>
       </c>
       <c r="O45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH45" s="3" t="s">
-        <v>3</v>
+      <c r="AH45" s="3">
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F46" s="3">
         <v>35900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>35500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>29800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>39900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>45600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>52600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>56900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>64700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>66700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>70500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>77100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>82600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>90900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>44000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>49200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>24000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>26100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>6400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>7800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>8700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>2300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>2100</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4245,11 +4454,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4320,8 +4529,14 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4329,10 +4544,10 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
@@ -4341,10 +4556,10 @@
         <v>400</v>
       </c>
       <c r="I48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K48" s="3">
         <v>500</v>
@@ -4353,28 +4568,28 @@
         <v>500</v>
       </c>
       <c r="M48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="O48" s="3">
         <v>700</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="Q48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="R48" s="3">
         <v>100</v>
       </c>
       <c r="S48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U48" s="3">
         <v>200</v>
@@ -4391,11 +4606,11 @@
       <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="Z48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>200</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -4406,11 +4621,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4421,8 +4636,14 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4510,11 +4731,11 @@
       <c r="AE49" s="3">
         <v>16500</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG49" s="3" t="s">
-        <v>3</v>
+      <c r="AF49" s="3">
+        <v>16500</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>16500</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>3</v>
@@ -4522,8 +4743,14 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,13 +4957,19 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -4768,11 +5007,11 @@
       <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -4786,11 +5025,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4825,8 +5064,14 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>39600</v>
+      </c>
+      <c r="F54" s="3">
         <v>52800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>52500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>46800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>57000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>62700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>69700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>74000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>81800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>83800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>87800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>94400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>99900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>107700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>60700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>65900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>40700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>42800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>23000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>23700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>24500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>25400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>27500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>23600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>17400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>17700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>18200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>18800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>18400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2100</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,145 +5360,153 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F57" s="3">
         <v>10600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
-      </c>
-      <c r="X57" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>500</v>
       </c>
       <c r="Z57" s="3">
         <v>500</v>
       </c>
       <c r="AA57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC57" s="3">
         <v>800</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>200</v>
       </c>
       <c r="AD57" s="3">
         <v>200</v>
       </c>
       <c r="AE57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH57" s="3" t="s">
-        <v>3</v>
+      <c r="AG57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>200</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>10000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>10100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,11 +5516,11 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5303,13 +5570,19 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
@@ -5324,240 +5597,252 @@
         <v>500</v>
       </c>
       <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>600</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
-      </c>
-      <c r="U59" s="3">
-        <v>400</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH59" s="3" t="s">
-        <v>3</v>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F60" s="3">
         <v>13800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>17500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>18500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>800</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>200</v>
       </c>
       <c r="AD60" s="3">
         <v>200</v>
       </c>
       <c r="AE60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF60" s="3">
         <v>200</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH60" s="3" t="s">
-        <v>3</v>
+      <c r="AG60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>200</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>14600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>14500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>14500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>14400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>14300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5606,8 +5891,14 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5623,38 +5914,38 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>100</v>
-      </c>
-      <c r="R62" s="3">
-        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5666,10 +5957,10 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X62" s="3">
         <v>200</v>
@@ -5677,11 +5968,11 @@
       <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>200</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5695,20 +5986,26 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH62" s="3">
         <v>100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F66" s="3">
         <v>14100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>18000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>19100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>21700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>19700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>17500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>800</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>200</v>
       </c>
       <c r="AD66" s="3">
         <v>200</v>
       </c>
       <c r="AE66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF66" s="3">
         <v>200</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH66" s="3" t="s">
-        <v>3</v>
+      <c r="AG66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>200</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6359,10 +6694,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>800</v>
@@ -6371,10 +6706,10 @@
         <v>800</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -6451,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-172800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-163100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-153900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-141800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-132000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-121000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-112600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-104100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-97600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-91000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-85200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-77500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-70600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-63700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-44600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-37900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-33400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-30200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-25500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-23300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-21300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-700</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>32100</v>
+      </c>
+      <c r="F76" s="3">
         <v>38700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>36300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>28200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>37300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>43900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>50700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>55300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>60100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>63700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>69900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>75600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>80200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>88300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>43200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>63600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>38800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>41200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>21700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>22400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>23600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>24700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>26800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>22900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>17500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>18000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>18600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>18100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1900</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-11000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-5800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>100</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,8 +7797,10 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7428,11 +7825,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7503,8 +7900,14 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-7000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-9800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,8 +8585,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8172,11 +8613,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8247,8 +8688,14 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,8 +8902,14 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8475,11 +8934,11 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -8550,8 +9009,14 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +9052,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8613,11 +9080,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8688,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,160 +9476,172 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F100" s="3">
         <v>9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>13000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>52900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>15000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>28500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>23200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>5000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>7300</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>900</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>1700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>400</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -9190,108 +9687,120 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="F102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>45000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>23400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>19500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>5900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,16 +820,16 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -840,22 +844,22 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -914,8 +918,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1021,25 +1028,28 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -1053,8 +1063,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -1128,8 +1138,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,115 +1180,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>6000</v>
       </c>
       <c r="J12" s="3">
         <v>6000</v>
       </c>
       <c r="K12" s="3">
-        <v>4100</v>
+        <v>6000</v>
       </c>
       <c r="L12" s="3">
         <v>4100</v>
       </c>
       <c r="M12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N12" s="3">
         <v>3400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>300</v>
       </c>
-      <c r="AH12" s="3">
-        <v>0</v>
-      </c>
       <c r="AI12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="3">
         <v>100</v>
       </c>
-      <c r="AK12" s="3" t="s">
+      <c r="AK12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,13 +1398,16 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>16500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1413,8 +1433,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1483,13 +1503,16 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-200</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E17" s="3">
         <v>10000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>6500</v>
       </c>
       <c r="L17" s="3">
         <v>6500</v>
       </c>
       <c r="M17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="N17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4800</v>
-      </c>
-      <c r="W17" s="3">
-        <v>2100</v>
       </c>
       <c r="X17" s="3">
         <v>2100</v>
       </c>
       <c r="Y17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1900</v>
       </c>
       <c r="AC17" s="3">
         <v>1900</v>
       </c>
       <c r="AD17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>-100</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-6400</v>
       </c>
       <c r="L18" s="3">
         <v>-6400</v>
       </c>
       <c r="M18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-6400</v>
       </c>
       <c r="P18" s="3">
         <v>-6400</v>
       </c>
       <c r="Q18" s="3">
-        <v>-9000</v>
+        <v>-6400</v>
       </c>
       <c r="R18" s="3">
         <v>-9000</v>
       </c>
       <c r="S18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T18" s="3">
         <v>-6600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4800</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-2100</v>
       </c>
       <c r="X18" s="3">
         <v>-2100</v>
       </c>
       <c r="Y18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC18" s="3">
         <v>-1900</v>
       </c>
       <c r="AD18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>100</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,56 +1917,57 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-300</v>
       </c>
       <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-500</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>-500</v>
       </c>
       <c r="M20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1944,11 +1978,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1988,43 +2022,46 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-10700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5900</v>
       </c>
       <c r="L21" s="3">
         <v>-5900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>-5900</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
@@ -2098,31 +2135,34 @@
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
@@ -2134,26 +2174,26 @@
         <v>600</v>
       </c>
       <c r="N22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
       </c>
       <c r="P22" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2205,115 +2245,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-6500</v>
       </c>
       <c r="L23" s="3">
         <v>-6500</v>
       </c>
       <c r="M23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N23" s="3">
         <v>-5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-2100</v>
       </c>
       <c r="X23" s="3">
         <v>-2100</v>
       </c>
       <c r="Y23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC23" s="3">
         <v>-1900</v>
       </c>
       <c r="AD23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AK23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2344,8 +2390,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2419,8 +2465,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-6500</v>
       </c>
       <c r="L26" s="3">
         <v>-6500</v>
       </c>
       <c r="M26" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N26" s="3">
         <v>-5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-2100</v>
       </c>
       <c r="X26" s="3">
         <v>-2100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC26" s="3">
         <v>-1900</v>
       </c>
       <c r="AD26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-6500</v>
       </c>
       <c r="L27" s="3">
         <v>-6500</v>
       </c>
       <c r="M27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N27" s="3">
         <v>-5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-2100</v>
       </c>
       <c r="X27" s="3">
         <v>-2100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC27" s="3">
         <v>-1900</v>
       </c>
       <c r="AD27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,56 +3235,59 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>300</v>
       </c>
       <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>500</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>500</v>
       </c>
       <c r="M32" s="3">
+        <v>500</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3228,11 +3298,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3272,118 +3342,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-6500</v>
       </c>
       <c r="L33" s="3">
         <v>-6500</v>
       </c>
       <c r="M33" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N33" s="3">
         <v>-5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-2100</v>
       </c>
       <c r="X33" s="3">
         <v>-2100</v>
       </c>
       <c r="Y33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC33" s="3">
         <v>-1900</v>
       </c>
       <c r="AD33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-6500</v>
       </c>
       <c r="L35" s="3">
         <v>-6500</v>
       </c>
       <c r="M35" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N35" s="3">
         <v>-5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-2100</v>
       </c>
       <c r="X35" s="3">
         <v>-2100</v>
       </c>
       <c r="Y35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC35" s="3">
         <v>-1900</v>
       </c>
       <c r="AD35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2" t="s">
+      <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3872,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E41" s="3">
         <v>19300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>61200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>74800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1800</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,13 +4090,16 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="E43" s="3">
         <v>1400</v>
@@ -4015,91 +4108,91 @@
         <v>1400</v>
       </c>
       <c r="G43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H43" s="3">
         <v>3400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>200</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>300</v>
       </c>
       <c r="AH43" s="3">
         <v>300</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>3</v>
+      <c r="AI43" s="3">
+        <v>300</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>3</v>
@@ -4107,8 +4200,11 @@
       <c r="AK43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4139,8 +4235,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4214,8 +4310,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4246,74 +4345,74 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>200</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
       <c r="W45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
       </c>
       <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI45" s="3" t="s">
-        <v>3</v>
+      <c r="AI45" s="3">
+        <v>0</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>3</v>
@@ -4321,115 +4420,121 @@
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E46" s="3">
         <v>21000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>52600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>64700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>66700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>70500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>77100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>82600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>90900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>49200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2100</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,8 +4565,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4535,13 +4640,16 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="3">
         <v>300</v>
@@ -4550,7 +4658,7 @@
         <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
@@ -4562,7 +4670,7 @@
         <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
@@ -4574,7 +4682,7 @@
         <v>500</v>
       </c>
       <c r="O48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="P48" s="3">
         <v>700</v>
@@ -4583,7 +4691,7 @@
         <v>700</v>
       </c>
       <c r="R48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="S48" s="3">
         <v>100</v>
@@ -4592,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="U48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V48" s="3">
         <v>200</v>
@@ -4612,8 +4720,8 @@
       <c r="AA48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>200</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4627,8 +4735,8 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4642,13 +4750,16 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>16500</v>
@@ -4737,8 +4848,8 @@
       <c r="AG49" s="3">
         <v>16500</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>3</v>
+      <c r="AH49" s="3">
+        <v>16500</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>3</v>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,16 +5080,19 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -5013,8 +5133,8 @@
       <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -5031,8 +5151,8 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -5070,8 +5190,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E54" s="3">
         <v>37800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>57000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>81800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>83800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>87800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>99900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>60700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>65900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2100</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,79 +5492,80 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>9300</v>
       </c>
       <c r="H57" s="3">
         <v>9300</v>
       </c>
       <c r="I57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1600</v>
       </c>
       <c r="U57" s="3">
         <v>1600</v>
       </c>
       <c r="V57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W57" s="3">
         <v>1200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>800</v>
       </c>
       <c r="X57" s="3">
         <v>800</v>
       </c>
       <c r="Y57" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z57" s="3">
         <v>700</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>500</v>
       </c>
       <c r="AA57" s="3">
         <v>500</v>
@@ -5443,10 +5574,10 @@
         <v>500</v>
       </c>
       <c r="AC57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD57" s="3">
         <v>800</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>200</v>
       </c>
       <c r="AE57" s="3">
         <v>200</v>
@@ -5455,61 +5586,64 @@
         <v>200</v>
       </c>
       <c r="AG57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>200</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
       </c>
       <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>10100</v>
       </c>
       <c r="K58" s="3">
         <v>10100</v>
       </c>
       <c r="L58" s="3">
+        <v>10100</v>
+      </c>
+      <c r="M58" s="3">
         <v>7600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5656,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5576,16 +5710,19 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
@@ -5603,28 +5740,28 @@
         <v>500</v>
       </c>
       <c r="K59" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L59" s="3">
         <v>600</v>
       </c>
       <c r="M59" s="3">
+        <v>600</v>
+      </c>
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>600</v>
       </c>
       <c r="S59" s="3">
         <v>600</v>
@@ -5633,20 +5770,20 @@
         <v>600</v>
       </c>
       <c r="U59" s="3">
+        <v>600</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
       <c r="Z59" s="3">
         <v>0</v>
       </c>
@@ -5654,11 +5791,11 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5668,14 +5805,14 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>3</v>
+      <c r="AI59" s="3">
+        <v>0</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>3</v>
@@ -5683,91 +5820,94 @@
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>500</v>
       </c>
       <c r="AA60" s="3">
         <v>500</v>
       </c>
       <c r="AB60" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="AC60" s="3">
         <v>800</v>
       </c>
       <c r="AD60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AE60" s="3">
         <v>200</v>
@@ -5776,22 +5916,25 @@
         <v>200</v>
       </c>
       <c r="AG60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH60" s="3">
         <v>300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>200</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5802,50 +5945,50 @@
         <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>300</v>
       </c>
       <c r="H61" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I61" s="3">
         <v>400</v>
       </c>
       <c r="J61" s="3">
+        <v>400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14600</v>
-      </c>
-      <c r="P61" s="3">
-        <v>14500</v>
       </c>
       <c r="Q61" s="3">
         <v>14500</v>
       </c>
       <c r="R61" s="3">
+        <v>14500</v>
+      </c>
+      <c r="S61" s="3">
         <v>14400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5897,8 +6040,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5920,35 +6066,35 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1100</v>
       </c>
       <c r="N62" s="3">
         <v>1100</v>
       </c>
       <c r="O62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="P62" s="3">
         <v>1000</v>
       </c>
       <c r="Q62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -5963,7 +6109,7 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
@@ -5974,8 +6120,8 @@
       <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
+      <c r="AB62" s="3">
+        <v>200</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
@@ -5992,20 +6138,23 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI62" s="3">
         <v>100</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,91 +6480,94 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E66" s="3">
         <v>8100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>700</v>
       </c>
       <c r="AA66" s="3">
         <v>700</v>
       </c>
       <c r="AB66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AC66" s="3">
         <v>800</v>
       </c>
       <c r="AD66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="AE66" s="3">
         <v>200</v>
@@ -6418,22 +6576,25 @@
         <v>200</v>
       </c>
       <c r="AG66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH66" s="3">
         <v>300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>200</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6700,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>800</v>
@@ -6712,7 +6880,7 @@
         <v>800</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-197300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-172800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-163100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-153900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-141800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-132000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-121000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-112600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-104100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-91000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-85200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-77500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-70600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-63700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-54000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-44600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-37900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-33400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-30200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-25500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-13600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E76" s="3">
         <v>29700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>38700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>55300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>69900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>88300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>43200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>63600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>22900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1900</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2" t="s">
+      <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-6500</v>
       </c>
       <c r="L81" s="3">
         <v>-6500</v>
       </c>
       <c r="M81" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N81" s="3">
         <v>-5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4700</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-2100</v>
       </c>
       <c r="X81" s="3">
         <v>-2100</v>
       </c>
       <c r="Y81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-1900</v>
       </c>
       <c r="AC81" s="3">
         <v>-1900</v>
       </c>
       <c r="AD81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7997,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7831,8 +8030,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7906,8 +8105,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI89" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AK89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,13 +8807,14 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-700</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -8619,8 +8840,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8694,8 +8915,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,13 +9135,16 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-700</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -8940,8 +9170,8 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9015,8 +9245,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9086,8 +9320,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,40 +9725,43 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-2500</v>
       </c>
       <c r="I100" s="3">
         <v>-2500</v>
       </c>
       <c r="J100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9524,32 +9770,32 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>52900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>15000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>28500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>23200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -9557,14 +9803,14 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>5000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7300</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -9572,37 +9818,40 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>900</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>400</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -9610,40 +9859,40 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
       </c>
       <c r="Q101" s="3">
         <v>100</v>
       </c>
       <c r="R101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -9693,114 +9942,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
-      <c r="AK101" s="3" t="s">
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-6000</v>
       </c>
       <c r="J102" s="3">
         <v>-6000</v>
       </c>
       <c r="K102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="L102" s="3">
         <v>-3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>45000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19500</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-1100</v>
       </c>
       <c r="X102" s="3">
         <v>-1100</v>
       </c>
       <c r="Y102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5900</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-500</v>
       </c>
       <c r="AD102" s="3">
         <v>-500</v>
       </c>
       <c r="AE102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>200</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
   <si>
     <t>INMB</t>
   </si>
@@ -656,193 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AO7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -854,26 +861,26 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -928,8 +935,14 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1041,34 +1054,40 @@
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1079,11 +1098,11 @@
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
@@ -1154,8 +1173,14 @@
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,121 +1220,129 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F12" s="3">
         <v>4800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J12" s="3">
         <v>10000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>7100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>8700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>6000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>6000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>5200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>7100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>6500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>4500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>2500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>900</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>800</v>
       </c>
       <c r="AA12" s="3">
         <v>900</v>
       </c>
       <c r="AB12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD12" s="3">
         <v>1200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>200</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>100</v>
       </c>
       <c r="AI12" s="3">
         <v>300</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="3">
         <v>100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>100</v>
       </c>
-      <c r="AM12" s="3" t="s">
+      <c r="AO12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1421,23 +1454,29 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>16500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,11 +1498,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1529,21 +1568,27 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>-200</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1647,8 +1692,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1685,234 +1736,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>12300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>11000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>9200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>9000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>6200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>-100</v>
       </c>
-      <c r="AM17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-8100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-9900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-12300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-11000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-8500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-6400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-6400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-9000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-6600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>100</v>
       </c>
-      <c r="AM18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1952,65 +2017,67 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
-        <v>-600</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
       </c>
       <c r="K20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -2018,14 +2085,14 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -2062,53 +2129,59 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
-      <c r="AM20" s="3" t="s">
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-8100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-11900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-10700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-6400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-8500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2178,8 +2251,14 @@
       <c r="AM21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2192,26 +2271,26 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>600</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
@@ -2220,13 +2299,13 @@
         <v>600</v>
       </c>
       <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>600</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>400</v>
       </c>
       <c r="S22" s="3">
         <v>500</v>
@@ -2235,14 +2314,14 @@
         <v>400</v>
       </c>
       <c r="U22" s="3">
+        <v>500</v>
+      </c>
+      <c r="V22" s="3">
+        <v>400</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,11 +2334,11 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2291,121 +2370,133 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-24500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-12100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-9700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-11000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-8600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-9700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-6700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>100</v>
       </c>
-      <c r="AM23" s="3" t="s">
+      <c r="AO23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2442,11 +2533,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2517,8 +2608,14 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2630,234 +2727,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-24500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-12100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-11000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-8600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-9500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>100</v>
       </c>
-      <c r="AM26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-24500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-12100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-8600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-9500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-4600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>100</v>
       </c>
-      <c r="AM27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2969,8 +3084,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3082,8 +3203,14 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3195,8 +3322,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3308,65 +3441,71 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
-        <v>600</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>-1000</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
       </c>
       <c r="K32" s="3">
+        <v>300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3374,14 +3513,14 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3418,124 +3557,136 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
-      <c r="AM32" s="3" t="s">
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-24500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-12100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-8600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-6700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>100</v>
       </c>
-      <c r="AM33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3647,239 +3798,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-24500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-12100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-8600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-6700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>100</v>
       </c>
-      <c r="AM35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2" t="s">
+      <c r="AO38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3919,8 +4088,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3960,121 +4131,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F41" s="3">
         <v>27700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>33400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>33600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>31100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>26000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>35800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>41800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>47800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>51000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>52200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>57400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>61200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>66700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>74800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>84500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>39500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>45300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>22000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>24300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>5900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>7000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>7400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>9400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>6000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1800</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4186,121 +4365,133 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1400</v>
       </c>
       <c r="H43" s="3">
         <v>1400</v>
       </c>
       <c r="I43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K43" s="3">
         <v>3400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>8500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>5100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>400</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>200</v>
       </c>
       <c r="AI43" s="3">
         <v>300</v>
       </c>
       <c r="AJ43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK43" s="3">
         <v>300</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL43" s="3" t="s">
-        <v>3</v>
+      <c r="AL43" s="3">
+        <v>300</v>
       </c>
       <c r="AM43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4337,11 +4528,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4412,8 +4603,14 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4450,196 +4647,208 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4300</v>
       </c>
       <c r="R45" s="3">
         <v>4700</v>
       </c>
       <c r="S45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="T45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>200</v>
       </c>
-      <c r="AJ45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL45" s="3" t="s">
-        <v>3</v>
+      <c r="AL45" s="3">
+        <v>0</v>
       </c>
       <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>29900</v>
+      </c>
+      <c r="F46" s="3">
         <v>30700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>36000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>35900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>35500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>39900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>45600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>52600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>56900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>64700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>66700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>70500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>77100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>82600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>90900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>44000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>49200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>24000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>26100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>6400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>7800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>8700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>10800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>7100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>2300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>2100</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4676,11 +4885,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4751,31 +4960,37 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G48" s="3">
         <v>1100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
       </c>
       <c r="I48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>400</v>
@@ -4784,10 +4999,10 @@
         <v>400</v>
       </c>
       <c r="M48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O48" s="3">
         <v>500</v>
@@ -4796,28 +5011,28 @@
         <v>500</v>
       </c>
       <c r="Q48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="R48" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="S48" s="3">
         <v>700</v>
       </c>
       <c r="T48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="U48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
       </c>
       <c r="W48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y48" s="3">
         <v>200</v>
@@ -4834,11 +5049,11 @@
       <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AD48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>200</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4849,11 +5064,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>0</v>
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK48" s="3">
         <v>0</v>
@@ -4864,8 +5079,14 @@
       <c r="AM48" s="3">
         <v>0</v>
       </c>
+      <c r="AN48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4876,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>16500</v>
@@ -4965,11 +5186,11 @@
       <c r="AI49" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK49" s="3" t="s">
-        <v>3</v>
+      <c r="AJ49" s="3">
+        <v>16500</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>16500</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>3</v>
@@ -4977,8 +5198,14 @@
       <c r="AM49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5090,8 +5317,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5203,8 +5436,14 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5215,13 +5454,13 @@
         <v>600</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -5259,11 +5498,11 @@
       <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
+        <v>100</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -5277,11 +5516,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -5316,8 +5555,14 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5429,121 +5674,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F54" s="3">
         <v>33400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>37700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>37800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>39600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>52800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>52500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>46800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>57000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>62700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>69700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>74000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>81800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>83800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>87800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>94400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>99900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>107700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>60700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>65900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>40700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>42800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>23000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>23700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>24500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>25400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>27500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>23600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>17400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>17700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>18200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>18800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>2100</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5583,8 +5840,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5624,169 +5883,177 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>500</v>
       </c>
       <c r="AD57" s="3">
         <v>500</v>
       </c>
       <c r="AE57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG57" s="3">
         <v>800</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>200</v>
       </c>
       <c r="AH57" s="3">
         <v>200</v>
       </c>
       <c r="AI57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ57" s="3">
         <v>200</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL57" s="3" t="s">
-        <v>3</v>
+      <c r="AK57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL57" s="3">
+        <v>200</v>
       </c>
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>10000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>10100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5796,11 +6063,11 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5850,25 +6117,31 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
-        <v>500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>600</v>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
         <v>500</v>
       </c>
       <c r="H59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I59" s="3">
         <v>500</v>
@@ -5883,264 +6156,276 @@
         <v>500</v>
       </c>
       <c r="M59" s="3">
+        <v>500</v>
+      </c>
+      <c r="N59" s="3">
+        <v>500</v>
+      </c>
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>600</v>
-      </c>
-      <c r="U59" s="3">
-        <v>600</v>
       </c>
       <c r="V59" s="3">
         <v>600</v>
       </c>
       <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y59" s="3">
         <v>200</v>
-      </c>
-      <c r="X59" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>400</v>
       </c>
       <c r="Z59" s="3">
         <v>300</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
       </c>
       <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3">
         <v>300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL59" s="3" t="s">
-        <v>3</v>
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="3">
+        <v>0</v>
       </c>
       <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F60" s="3">
         <v>7400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>15100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>17500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>800</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>200</v>
       </c>
       <c r="AH60" s="3">
         <v>200</v>
       </c>
       <c r="AI60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ60" s="3">
         <v>200</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL60" s="3" t="s">
-        <v>3</v>
+      <c r="AK60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL60" s="3">
+        <v>200</v>
       </c>
       <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>400</v>
+      </c>
+      <c r="F61" s="3">
         <v>600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>200</v>
       </c>
       <c r="H61" s="3">
+        <v>200</v>
+      </c>
+      <c r="I61" s="3">
+        <v>200</v>
+      </c>
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>14600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>14500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>14500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>14400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>14300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -6189,8 +6474,14 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6218,38 +6509,38 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>100</v>
-      </c>
-      <c r="V62" s="3">
-        <v>100</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -6261,10 +6552,10 @@
         <v>100</v>
       </c>
       <c r="Z62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB62" s="3">
         <v>200</v>
@@ -6272,11 +6563,11 @@
       <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
+      <c r="AD62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>200</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
@@ -6290,20 +6581,26 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL62" s="3">
         <v>100</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6415,8 +6712,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6528,8 +6831,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6641,121 +6950,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8000</v>
+        <v>6200</v>
       </c>
       <c r="E66" s="3">
         <v>8800</v>
       </c>
       <c r="F66" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>8800</v>
+      </c>
+      <c r="H66" s="3">
         <v>8100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>18000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>21700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>17900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>18700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>19700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>17500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>800</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>200</v>
       </c>
       <c r="AH66" s="3">
         <v>200</v>
       </c>
       <c r="AI66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ66" s="3">
         <v>200</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL66" s="3" t="s">
-        <v>3</v>
+      <c r="AK66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL66" s="3">
+        <v>200</v>
       </c>
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6795,8 +7116,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6908,8 +7231,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7021,8 +7350,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7042,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>800</v>
@@ -7054,10 +7389,10 @@
         <v>800</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -7134,8 +7469,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7247,121 +7588,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-214400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-203800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-197300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-172800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-163100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-153900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-141800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-132000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-121000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-112600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-104100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-97600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-91000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-85200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-77500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-70600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-63700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-54000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-44600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-37900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-33400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-30200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-15900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-700</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7473,8 +7826,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7586,8 +7945,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7699,121 +8064,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F76" s="3">
         <v>25400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>28900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>29700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>32100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>38700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>36300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>28200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>37300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>43900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>50700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>55300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>60100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>63700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>69900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>75600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>80200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>88300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>43200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>63600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>38800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>41200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>21700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>22400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>24700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>26800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>22900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>16500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>17500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>18000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>18600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>1900</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7925,239 +8302,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2" t="s">
+      <c r="AO80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-24500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-12100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-8600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-6700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>100</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8197,8 +8592,10 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8235,11 +8632,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -8310,8 +8707,14 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8423,8 +8826,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8536,8 +8945,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8649,8 +9064,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8762,8 +9183,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8875,121 +9302,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-7900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-4800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-9800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-7900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-100</v>
       </c>
-      <c r="AM89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9029,23 +9468,25 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
@@ -9067,11 +9508,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9142,8 +9583,14 @@
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9255,8 +9702,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9368,23 +9821,29 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
@@ -9406,11 +9865,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -9481,8 +9940,14 @@
       <c r="AM94" s="3">
         <v>0</v>
       </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9522,8 +9987,10 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9560,11 +10027,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9635,8 +10102,14 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9748,8 +10221,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9861,8 +10340,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9974,184 +10459,196 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>22300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>5300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>9800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>52900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>15000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>28500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>23200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>5000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>7300</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>900</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>1700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>400</v>
       </c>
-      <c r="AM100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -10197,120 +10694,132 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
-      <c r="AM101" s="3" t="s">
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>14000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-12600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>5100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-8100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-9700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>45000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-5800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>23400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>19500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>3300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>5900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>1600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>200</v>
       </c>
-      <c r="AM102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
